--- a/src/components/study/excel/topics/statistical-functions-analysis/excel_files/statistical_functions.xlsx
+++ b/src/components/study/excel/topics/statistical-functions-analysis/excel_files/statistical_functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\React Project\react_routing_tailwind\src\components\study\excel\topics\statistical-functions-analysis\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030D546C-0A5A-4F88-9681-054328C6FAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81936ED7-7027-46C3-8623-27E94F7BA82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" firstSheet="5" activeTab="16" xr2:uid="{3601E814-DA2A-47C5-8CA9-3A7140510189}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" firstSheet="27" activeTab="37" xr2:uid="{3601E814-DA2A-47C5-8CA9-3A7140510189}"/>
   </bookViews>
   <sheets>
     <sheet name="CNAT" sheetId="12" r:id="rId1"/>
@@ -30,6 +30,27 @@
     <sheet name="mode_mult_data" sheetId="15" r:id="rId15"/>
     <sheet name="stdev_s_data" sheetId="16" r:id="rId16"/>
     <sheet name="stdev_p_data" sheetId="17" r:id="rId17"/>
+    <sheet name="var_s_data" sheetId="18" r:id="rId18"/>
+    <sheet name="var_p_data" sheetId="19" r:id="rId19"/>
+    <sheet name="large_data" sheetId="20" r:id="rId20"/>
+    <sheet name="small_data" sheetId="21" r:id="rId21"/>
+    <sheet name="rank_eq_data" sheetId="22" r:id="rId22"/>
+    <sheet name="rank_avg_data" sheetId="23" r:id="rId23"/>
+    <sheet name="quartile_inc_data" sheetId="24" r:id="rId24"/>
+    <sheet name="quartile_exc_data" sheetId="25" r:id="rId25"/>
+    <sheet name="percentile_inc_data" sheetId="26" r:id="rId26"/>
+    <sheet name="percentile_exc_data" sheetId="27" r:id="rId27"/>
+    <sheet name="percentrank_inc_data" sheetId="28" r:id="rId28"/>
+    <sheet name="percentrank_exc_data" sheetId="29" r:id="rId29"/>
+    <sheet name="correl_data" sheetId="30" r:id="rId30"/>
+    <sheet name="forecast_linear_data" sheetId="31" r:id="rId31"/>
+    <sheet name="trend_data" sheetId="32" r:id="rId32"/>
+    <sheet name="iferror_data" sheetId="33" r:id="rId33"/>
+    <sheet name="missing_data" sheetId="34" r:id="rId34"/>
+    <sheet name="outlier_data" sheetId="35" r:id="rId35"/>
+    <sheet name="combine_if_data" sheetId="36" r:id="rId36"/>
+    <sheet name="practice_multi_data" sheetId="37" r:id="rId37"/>
+    <sheet name="real_dataset" sheetId="38" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="168">
   <si>
     <t>Student</t>
   </si>
@@ -388,6 +409,177 @@
   </si>
   <si>
     <t>Jun</t>
+  </si>
+  <si>
+    <t>SampleID</t>
+  </si>
+  <si>
+    <t>PopulationFlag</t>
+  </si>
+  <si>
+    <t>Sample_A</t>
+  </si>
+  <si>
+    <t>Sample_B</t>
+  </si>
+  <si>
+    <t>Sample_C</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>PopulationID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Census</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>All_Students</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>Full_Sales</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Kunal</t>
+  </si>
+  <si>
+    <t>DailySales</t>
+  </si>
+  <si>
+    <t>Product_A</t>
+  </si>
+  <si>
+    <t>Product_B</t>
+  </si>
+  <si>
+    <t>Product_C</t>
+  </si>
+  <si>
+    <t>Product_D</t>
+  </si>
+  <si>
+    <t>Product_E</t>
+  </si>
+  <si>
+    <t>Product_F</t>
+  </si>
+  <si>
+    <t>Product_G</t>
+  </si>
+  <si>
+    <t>Product_H</t>
+  </si>
+  <si>
+    <t>Product_I</t>
+  </si>
+  <si>
+    <t>Product_J</t>
+  </si>
+  <si>
+    <t>StudentID</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Outlier</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>AdsSpend</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>AdSpend_K</t>
+  </si>
+  <si>
+    <t>ActualSales_K</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>AdSpend</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Attendance (1/0)</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Customer_Score</t>
+  </si>
+  <si>
+    <t>Return_Flag</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -431,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -441,6 +633,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2536,6 +2729,435 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{755C9B8A-A1D2-4A76-AB42-104C29D84CED}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>96</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BE4F7F-1BA3-4854-9529-CEBDE966A330}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2">
+        <v>55000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3">
+        <v>52000</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4">
+        <v>58000</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5">
+        <v>54000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6">
+        <v>56000</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12">
+        <v>1200</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13">
+        <v>1150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14">
+        <v>1300</v>
+      </c>
+      <c r="C14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15">
+        <v>1250</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16">
+        <v>1180</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD9640B-1050-4991-87F5-8CE9C53A39F7}">
   <dimension ref="A1:B6"/>
@@ -2591,6 +3213,2552 @@
       </c>
       <c r="B6" s="2">
         <v>1800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE7A7C0-F215-4C4E-9760-6929350B9E38}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9D25C7-453D-451C-85D3-117CBC249BE7}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2">
+        <v>120</v>
+      </c>
+      <c r="C2">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3">
+        <v>135</v>
+      </c>
+      <c r="C3">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4">
+        <v>90</v>
+      </c>
+      <c r="C4">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5">
+        <v>150</v>
+      </c>
+      <c r="C5">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6">
+        <v>110</v>
+      </c>
+      <c r="C6">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7">
+        <v>140</v>
+      </c>
+      <c r="C7">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8">
+        <v>125</v>
+      </c>
+      <c r="C8">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10">
+        <v>145</v>
+      </c>
+      <c r="C10">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11">
+        <v>115</v>
+      </c>
+      <c r="C11">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF5331F-1AF4-4E3A-A132-5C4FEB9B6A3D}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>95</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>78</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8613EF00-DA4E-4931-BE75-6639D9A0E548}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>95</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>78</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11">
+        <v>95</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B50991-95F6-4108-A415-C4773F956DA1}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>1300</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>97</v>
+      </c>
+      <c r="C13">
+        <v>1600</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>1050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>89</v>
+      </c>
+      <c r="C15">
+        <v>1380</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>93</v>
+      </c>
+      <c r="C16">
+        <v>1480</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>1220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>77</v>
+      </c>
+      <c r="C18">
+        <v>850</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>90</v>
+      </c>
+      <c r="C19">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>1280</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>81</v>
+      </c>
+      <c r="C21">
+        <v>1120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6EAA081-A3EE-46FC-BB9A-44BC4FEFE89E}">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3706EA-6015-454E-8EAD-89048CEEDA92}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="4">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="4">
+        <v>45675</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="4">
+        <v>45677</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="4">
+        <v>45679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="4">
+        <v>45682</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="4">
+        <v>45685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="4">
+        <v>45687</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>1300</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="4">
+        <v>45691</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>97</v>
+      </c>
+      <c r="C13">
+        <v>1600</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>45693</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>1050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="4">
+        <v>45695</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>89</v>
+      </c>
+      <c r="C15">
+        <v>1380</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="4">
+        <v>45697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>93</v>
+      </c>
+      <c r="C16">
+        <v>1480</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="4">
+        <v>45699</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>1220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="4">
+        <v>45701</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>77</v>
+      </c>
+      <c r="C18">
+        <v>850</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="4">
+        <v>45703</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>90</v>
+      </c>
+      <c r="C19">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="4">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>1280</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="4">
+        <v>45707</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>81</v>
+      </c>
+      <c r="C21">
+        <v>1120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="4">
+        <v>45709</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF8515A-BF24-48E4-BD68-F9CD9E7E53ED}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>1300</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>97</v>
+      </c>
+      <c r="C13">
+        <v>1600</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>1050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>89</v>
+      </c>
+      <c r="C15">
+        <v>1380</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>93</v>
+      </c>
+      <c r="C16">
+        <v>1480</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>1220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>77</v>
+      </c>
+      <c r="C18">
+        <v>850</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>90</v>
+      </c>
+      <c r="C19">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>1280</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>81</v>
+      </c>
+      <c r="C21">
+        <v>1120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>300</v>
+      </c>
+      <c r="C22">
+        <v>5000</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102CCF8A-D850-42C4-B917-BA10D1D9DF2B}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>1300</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>97</v>
+      </c>
+      <c r="C13">
+        <v>1600</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>1050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>89</v>
+      </c>
+      <c r="C15">
+        <v>1380</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>93</v>
+      </c>
+      <c r="C16">
+        <v>1480</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>1220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>77</v>
+      </c>
+      <c r="C18">
+        <v>850</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>90</v>
+      </c>
+      <c r="C19">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>1280</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>81</v>
+      </c>
+      <c r="C21">
+        <v>1120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4BF004-7C9B-4C24-89FF-142A6A01C36E}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>25000</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>28000</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>32000</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>35000</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>40000</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>45000</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>50000</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>60000</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>75000</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>82000</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>79000</v>
+      </c>
+      <c r="C12">
+        <v>1300</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>97000</v>
+      </c>
+      <c r="C13">
+        <v>1600</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>65000</v>
+      </c>
+      <c r="C14">
+        <v>1050</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>89000</v>
+      </c>
+      <c r="C15">
+        <v>1380</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>93000</v>
+      </c>
+      <c r="C16">
+        <v>1480</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>84000</v>
+      </c>
+      <c r="C17">
+        <v>1220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>77000</v>
+      </c>
+      <c r="C18">
+        <v>850</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>90000</v>
+      </c>
+      <c r="C19">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>86000</v>
+      </c>
+      <c r="C20">
+        <v>1280</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>81000</v>
+      </c>
+      <c r="C21">
+        <v>1120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2689,6 +5857,2151 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8AE388C-6CE4-4C5F-8487-B0FF914BC813}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>85</v>
+      </c>
+      <c r="D2">
+        <v>1200</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>92</v>
+      </c>
+      <c r="D3">
+        <v>1350</v>
+      </c>
+      <c r="E3">
+        <v>250</v>
+      </c>
+      <c r="F3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>78</v>
+      </c>
+      <c r="D4">
+        <v>900</v>
+      </c>
+      <c r="E4">
+        <v>150</v>
+      </c>
+      <c r="F4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>95</v>
+      </c>
+      <c r="D5">
+        <v>1500</v>
+      </c>
+      <c r="E5">
+        <v>300</v>
+      </c>
+      <c r="F5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>68</v>
+      </c>
+      <c r="D6">
+        <v>1100</v>
+      </c>
+      <c r="E6">
+        <v>180</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>88</v>
+      </c>
+      <c r="D7">
+        <v>1400</v>
+      </c>
+      <c r="E7">
+        <v>260</v>
+      </c>
+      <c r="F7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>91</v>
+      </c>
+      <c r="D8">
+        <v>1250</v>
+      </c>
+      <c r="E8">
+        <v>220</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>76</v>
+      </c>
+      <c r="D9">
+        <v>800</v>
+      </c>
+      <c r="E9">
+        <v>130</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>94</v>
+      </c>
+      <c r="D10">
+        <v>1450</v>
+      </c>
+      <c r="E10">
+        <v>280</v>
+      </c>
+      <c r="F10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>86</v>
+      </c>
+      <c r="D11">
+        <v>1150</v>
+      </c>
+      <c r="E11">
+        <v>190</v>
+      </c>
+      <c r="F11">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B97AC0-E318-4AD5-901A-C124F0145A3E}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>610185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>711198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>812210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>913225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>1014240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7777F925-CE07-4542-AE60-7E79BFF10405}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>120</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>135</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>150</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>170</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>190</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>205</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>225</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>240</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>260</v>
+      </c>
+      <c r="C11">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6CB030-25AB-4311-BAEF-52B64067DB3F}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DD8310-0C0E-45EF-BF72-71BDD8D8E47C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>78</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F95C69E2-8C70-4116-93CC-866BE2266C4D}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10.1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="C3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>9.9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>10.1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="C9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>10.1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>10.3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3406666C-4DEF-40BC-82AE-95D23326E26C}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>1350</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>95</v>
+      </c>
+      <c r="C5">
+        <v>1500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>1100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>1400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>1450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>1150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D26C5B7-8B3F-424E-BD4D-903A08D7EC0D}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2">
+        <v>45000</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45667</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>85</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45669</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3">
+        <v>92</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>2500</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4">
+        <v>45672</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4">
+        <v>78</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>8000</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>45675</v>
+      </c>
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>95</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>600</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4">
+        <v>45677</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6">
+        <v>68</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7">
+        <v>450</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4">
+        <v>45679</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>88</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>300</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>45682</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>91</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>48000</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>45685</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9">
+        <v>76</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10">
+        <v>1350</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4">
+        <v>45687</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>94</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11">
+        <v>620</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4">
+        <v>45689</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>82</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>480</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4">
+        <v>45691</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>79</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13">
+        <v>280</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>45693</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>97</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB2E14E-80F8-4B49-AE90-2F8078C04B63}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>45662</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2">
+        <v>600</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3">
+        <v>450</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>45667</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>750</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>45669</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>45672</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6">
+        <v>45000</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>45675</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>1200</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>45677</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>2500</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>45679</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>8000</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>45682</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10">
+        <v>620</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>45685</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>480</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>45687</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12">
+        <v>280</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>45690</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13">
+        <v>48000</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>45693</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14">
+        <v>1350</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>45696</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15">
+        <v>2500</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>7</v>
+      </c>
+      <c r="G15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>45698</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16">
+        <v>8000</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>45700</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>600</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>45703</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18">
+        <v>450</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>45706</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>750</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>45708</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20">
+        <v>300</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>45710</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>45000</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>45713</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22">
+        <v>1200</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="G22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>45716</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23">
+        <v>2500</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>45718</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24">
+        <v>8000</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>45721</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25">
+        <v>620</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>45724</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26">
+        <v>480</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>45726</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27">
+        <v>280</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>45728</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28">
+        <v>45000</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>45731</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>1200</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="G29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>45734</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30">
+        <v>2500</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>45736</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31">
+        <v>8000</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
